--- a/course-design-2/outputs/tables/ch4/30_recruitment_lifecycle_statistics.xlsx
+++ b/course-design-2/outputs/tables/ch4/30_recruitment_lifecycle_statistics.xlsx
@@ -670,7 +670,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
